--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574989373</v>
+        <v>46157.93119131516</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119131516</v>
+        <v>46157.93184392391</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184392391</v>
+        <v>46157.93406369082</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406369082</v>
+        <v>46157.9372440037</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372440037</v>
+        <v>46158.28222108928</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222108928</v>
+        <v>46158.29703516416</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29703516416</v>
+        <v>46158.29821965539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821965539</v>
+        <v>46158.3339306729</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339306729</v>
+        <v>46158.36862849934</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Родионов- механик/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862849934</v>
+        <v>46158.37293821197</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
